--- a/dev/results_by_follow.xlsx
+++ b/dev/results_by_follow.xlsx
@@ -1,20 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vladi\Documents\stocks_entry_prediction\dev\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF1D5CB-559E-4BEC-8D4B-AC9FE91B475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4080" yWindow="4065" windowWidth="17250" windowHeight="8865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="oct24" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>DATE</t>
   </si>
@@ -60,15 +78,57 @@
   <si>
     <t>TOTAL_PROFIT</t>
   </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>SL Size</t>
+  </si>
+  <si>
+    <t>TP Size</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Open Price</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>Close Price</t>
+  </si>
+  <si>
+    <t>Financial result</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +138,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -117,28 +184,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -176,9 +257,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -210,9 +291,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,9 +343,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -419,11 +536,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P431"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +587,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>14</v>
       </c>
@@ -520,7 +637,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>15</v>
       </c>
@@ -546,7 +663,7 @@
         <v>658238</v>
       </c>
       <c r="I3">
-        <v>1207.41</v>
+        <v>1207.4100000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -570,7 +687,7 @@
         <v>-233</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>16</v>
       </c>
@@ -596,7 +713,7 @@
         <v>767748</v>
       </c>
       <c r="I4">
-        <v>1161.59</v>
+        <v>1161.5899999999999</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -620,7 +737,7 @@
         <v>-230</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>17</v>
       </c>
@@ -670,7 +787,7 @@
         <v>-242</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>18</v>
       </c>
@@ -720,7 +837,7 @@
         <v>-382</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>19</v>
       </c>
@@ -770,7 +887,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>20</v>
       </c>
@@ -796,7 +913,7 @@
         <v>1274234</v>
       </c>
       <c r="I8">
-        <v>1115.36</v>
+        <v>1115.3599999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -820,7 +937,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>21</v>
       </c>
@@ -846,7 +963,7 @@
         <v>781263</v>
       </c>
       <c r="I9">
-        <v>1078.4</v>
+        <v>1078.4000000000001</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -870,7 +987,7 @@
         <v>-109</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>22</v>
       </c>
@@ -896,7 +1013,7 @@
         <v>849914</v>
       </c>
       <c r="I10">
-        <v>1066.37</v>
+        <v>1066.3699999999999</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -920,7 +1037,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>23</v>
       </c>
@@ -970,7 +1087,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24</v>
       </c>
@@ -1020,7 +1137,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>25</v>
       </c>
@@ -1070,7 +1187,7 @@
         <v>-306</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>26</v>
       </c>
@@ -1120,7 +1237,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>27</v>
       </c>
@@ -1170,7 +1287,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>28</v>
       </c>
@@ -1220,7 +1337,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>29</v>
       </c>
@@ -1270,7 +1387,7 @@
         <v>-260</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>30</v>
       </c>
@@ -1320,7 +1437,7 @@
         <v>-309</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>31</v>
       </c>
@@ -1370,7 +1487,7 @@
         <v>-593</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>32</v>
       </c>
@@ -1420,7 +1537,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>33</v>
       </c>
@@ -1470,7 +1587,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>34</v>
       </c>
@@ -1520,7 +1637,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>35</v>
       </c>
@@ -1546,7 +1663,7 @@
         <v>1147529</v>
       </c>
       <c r="I23">
-        <v>1096.37</v>
+        <v>1096.3699999999999</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1570,7 +1687,7 @@
         <v>-104</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>36</v>
       </c>
@@ -1620,7 +1737,7 @@
         <v>-461</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>37</v>
       </c>
@@ -1670,7 +1787,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>38</v>
       </c>
@@ -1696,7 +1813,7 @@
         <v>1396546</v>
       </c>
       <c r="I26">
-        <v>1212.63</v>
+        <v>1212.6300000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1720,7 +1837,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>39</v>
       </c>
@@ -1770,7 +1887,7 @@
         <v>-562</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>40</v>
       </c>
@@ -1820,7 +1937,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>41</v>
       </c>
@@ -1870,7 +1987,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>42</v>
       </c>
@@ -1896,7 +2013,7 @@
         <v>878501</v>
       </c>
       <c r="I30">
-        <v>1115.64</v>
+        <v>1115.6400000000001</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1920,7 +2037,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>43</v>
       </c>
@@ -1970,7 +2087,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>44</v>
       </c>
@@ -1996,7 +2113,7 @@
         <v>888399</v>
       </c>
       <c r="I32">
-        <v>1106.34</v>
+        <v>1106.3399999999999</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2020,7 +2137,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45</v>
       </c>
@@ -2070,7 +2187,7 @@
         <v>-137</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46</v>
       </c>
@@ -2120,7 +2237,7 @@
         <v>-263</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>47</v>
       </c>
@@ -2170,7 +2287,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>48</v>
       </c>
@@ -2220,7 +2337,7 @@
         <v>-563</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>49</v>
       </c>
@@ -2246,7 +2363,7 @@
         <v>568509</v>
       </c>
       <c r="I37">
-        <v>990.0599999999999</v>
+        <v>990.06</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2270,7 +2387,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>50</v>
       </c>
@@ -2320,7 +2437,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>51</v>
       </c>
@@ -2370,7 +2487,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>52</v>
       </c>
@@ -2420,7 +2537,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>53</v>
       </c>
@@ -2470,7 +2587,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>54</v>
       </c>
@@ -2520,7 +2637,7 @@
         <v>-565</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>55</v>
       </c>
@@ -2570,7 +2687,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>56</v>
       </c>
@@ -2620,7 +2737,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>57</v>
       </c>
@@ -2670,7 +2787,7 @@
         <v>-293</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>58</v>
       </c>
@@ -2720,7 +2837,7 @@
         <v>-511</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>59</v>
       </c>
@@ -2770,7 +2887,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>60</v>
       </c>
@@ -2820,7 +2937,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>61</v>
       </c>
@@ -2846,7 +2963,7 @@
         <v>883275</v>
       </c>
       <c r="I49">
-        <v>954.8099999999999</v>
+        <v>954.81</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2870,7 +2987,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>62</v>
       </c>
@@ -2896,7 +3013,7 @@
         <v>834545</v>
       </c>
       <c r="I50">
-        <v>996.6799999999999</v>
+        <v>996.68</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2920,7 +3037,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>63</v>
       </c>
@@ -2970,7 +3087,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>64</v>
       </c>
@@ -2996,7 +3113,7 @@
         <v>770103</v>
       </c>
       <c r="I52">
-        <v>975.4400000000001</v>
+        <v>975.44</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -3020,7 +3137,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>65</v>
       </c>
@@ -3046,7 +3163,7 @@
         <v>1128114</v>
       </c>
       <c r="I53">
-        <v>1025.62</v>
+        <v>1025.6199999999999</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -3070,7 +3187,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>66</v>
       </c>
@@ -3120,7 +3237,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>67</v>
       </c>
@@ -3146,7 +3263,7 @@
         <v>1700100</v>
       </c>
       <c r="I55">
-        <v>1141.09</v>
+        <v>1141.0899999999999</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -3170,7 +3287,7 @@
         <v>-323</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>68</v>
       </c>
@@ -3196,7 +3313,7 @@
         <v>944263</v>
       </c>
       <c r="I56">
-        <v>1148.15</v>
+        <v>1148.1500000000001</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -3220,7 +3337,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>69</v>
       </c>
@@ -3270,7 +3387,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>70</v>
       </c>
@@ -3320,7 +3437,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>71</v>
       </c>
@@ -3370,7 +3487,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>72</v>
       </c>
@@ -3420,7 +3537,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>73</v>
       </c>
@@ -3446,7 +3563,7 @@
         <v>685353</v>
       </c>
       <c r="I61">
-        <v>1098.09</v>
+        <v>1098.0899999999999</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3470,7 +3587,7 @@
         <v>-316</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>74</v>
       </c>
@@ -3520,7 +3637,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>75</v>
       </c>
@@ -3546,7 +3663,7 @@
         <v>868579</v>
       </c>
       <c r="I63">
-        <v>1078.15</v>
+        <v>1078.1500000000001</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3570,7 +3687,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>76</v>
       </c>
@@ -3596,7 +3713,7 @@
         <v>591377</v>
       </c>
       <c r="I64">
-        <v>1047.64</v>
+        <v>1047.6400000000001</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -3620,7 +3737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>77</v>
       </c>
@@ -3646,7 +3763,7 @@
         <v>812121</v>
       </c>
       <c r="I65">
-        <v>1030.38</v>
+        <v>1030.3800000000001</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -3670,7 +3787,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>78</v>
       </c>
@@ -3720,7 +3837,7 @@
         <v>-306</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>79</v>
       </c>
@@ -3770,7 +3887,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>80</v>
       </c>
@@ -3820,7 +3937,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>81</v>
       </c>
@@ -3870,7 +3987,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>82</v>
       </c>
@@ -3896,7 +4013,7 @@
         <v>1168695</v>
       </c>
       <c r="I70">
-        <v>1132.61</v>
+        <v>1132.6099999999999</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -3920,7 +4037,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>83</v>
       </c>
@@ -3970,7 +4087,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>84</v>
       </c>
@@ -4020,7 +4137,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>85</v>
       </c>
@@ -4070,7 +4187,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>86</v>
       </c>
@@ -4120,7 +4237,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>87</v>
       </c>
@@ -4170,7 +4287,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>88</v>
       </c>
@@ -4220,7 +4337,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>89</v>
       </c>
@@ -4270,7 +4387,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>90</v>
       </c>
@@ -4320,7 +4437,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>91</v>
       </c>
@@ -4370,7 +4487,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>92</v>
       </c>
@@ -4420,7 +4537,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>93</v>
       </c>
@@ -4470,7 +4587,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>94</v>
       </c>
@@ -4520,7 +4637,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>95</v>
       </c>
@@ -4570,7 +4687,7 @@
         <v>-213</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>96</v>
       </c>
@@ -4620,7 +4737,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>97</v>
       </c>
@@ -4670,7 +4787,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>98</v>
       </c>
@@ -4696,7 +4813,7 @@
         <v>850172</v>
       </c>
       <c r="I86">
-        <v>1249.15</v>
+        <v>1249.1500000000001</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -4720,7 +4837,7 @@
         <v>-83</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>99</v>
       </c>
@@ -4770,7 +4887,7 @@
         <v>-102</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>100</v>
       </c>
@@ -4820,7 +4937,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>101</v>
       </c>
@@ -4870,7 +4987,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>102</v>
       </c>
@@ -4920,7 +5037,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>103</v>
       </c>
@@ -4946,7 +5063,7 @@
         <v>993678</v>
       </c>
       <c r="I91">
-        <v>1137.62</v>
+        <v>1137.6199999999999</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4970,7 +5087,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>104</v>
       </c>
@@ -4996,7 +5113,7 @@
         <v>1016842</v>
       </c>
       <c r="I92">
-        <v>1136.65</v>
+        <v>1136.6500000000001</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -5020,7 +5137,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>105</v>
       </c>
@@ -5070,7 +5187,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>106</v>
       </c>
@@ -5120,7 +5237,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>107</v>
       </c>
@@ -5170,7 +5287,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>108</v>
       </c>
@@ -5220,7 +5337,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>109</v>
       </c>
@@ -5270,7 +5387,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>110</v>
       </c>
@@ -5296,7 +5413,7 @@
         <v>1705968</v>
       </c>
       <c r="I98">
-        <v>1167.41</v>
+        <v>1167.4100000000001</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -5320,7 +5437,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>111</v>
       </c>
@@ -5370,7 +5487,7 @@
         <v>-76</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>112</v>
       </c>
@@ -5420,7 +5537,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>113</v>
       </c>
@@ -5446,7 +5563,7 @@
         <v>997870</v>
       </c>
       <c r="I101">
-        <v>1192.61</v>
+        <v>1192.6099999999999</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -5470,7 +5587,7 @@
         <v>-567</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>114</v>
       </c>
@@ -5496,7 +5613,7 @@
         <v>889227</v>
       </c>
       <c r="I102">
-        <v>1170.14</v>
+        <v>1170.1400000000001</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5520,7 +5637,7 @@
         <v>-133</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>115</v>
       </c>
@@ -5570,7 +5687,7 @@
         <v>-748</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>116</v>
       </c>
@@ -5620,7 +5737,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>117</v>
       </c>
@@ -5646,7 +5763,7 @@
         <v>1073910</v>
       </c>
       <c r="I105">
-        <v>1211.35</v>
+        <v>1211.3499999999999</v>
       </c>
       <c r="J105">
         <v>1</v>
@@ -5670,7 +5787,7 @@
         <v>-310</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>118</v>
       </c>
@@ -5720,7 +5837,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>119</v>
       </c>
@@ -5770,7 +5887,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>120</v>
       </c>
@@ -5796,7 +5913,7 @@
         <v>829207</v>
       </c>
       <c r="I108">
-        <v>1277.89</v>
+        <v>1277.8900000000001</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -5820,7 +5937,7 @@
         <v>-181</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>121</v>
       </c>
@@ -5870,7 +5987,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>122</v>
       </c>
@@ -5920,7 +6037,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>123</v>
       </c>
@@ -5970,7 +6087,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>124</v>
       </c>
@@ -6020,7 +6137,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>125</v>
       </c>
@@ -6070,7 +6187,7 @@
         <v>-572</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>126</v>
       </c>
@@ -6120,7 +6237,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>127</v>
       </c>
@@ -6170,7 +6287,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>128</v>
       </c>
@@ -6220,7 +6337,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>129</v>
       </c>
@@ -6270,7 +6387,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>130</v>
       </c>
@@ -6320,7 +6437,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>131</v>
       </c>
@@ -6370,7 +6487,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>132</v>
       </c>
@@ -6420,7 +6537,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>133</v>
       </c>
@@ -6470,7 +6587,7 @@
         <v>-615</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>134</v>
       </c>
@@ -6520,7 +6637,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>135</v>
       </c>
@@ -6570,7 +6687,7 @@
         <v>-282</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>136</v>
       </c>
@@ -6620,7 +6737,7 @@
         <v>-256</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>137</v>
       </c>
@@ -6670,7 +6787,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>138</v>
       </c>
@@ -6720,7 +6837,7 @@
         <v>-665</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>139</v>
       </c>
@@ -6770,7 +6887,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>140</v>
       </c>
@@ -6796,7 +6913,7 @@
         <v>666516</v>
       </c>
       <c r="I128">
-        <v>1307.85</v>
+        <v>1307.8499999999999</v>
       </c>
       <c r="J128">
         <v>1</v>
@@ -6820,7 +6937,7 @@
         <v>-140</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>141</v>
       </c>
@@ -6870,7 +6987,7 @@
         <v>-184</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>142</v>
       </c>
@@ -6896,7 +7013,7 @@
         <v>1009033</v>
       </c>
       <c r="I130">
-        <v>1236.6</v>
+        <v>1236.5999999999999</v>
       </c>
       <c r="J130">
         <v>1</v>
@@ -6920,7 +7037,7 @@
         <v>-545</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>143</v>
       </c>
@@ -6970,7 +7087,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>144</v>
       </c>
@@ -7020,7 +7137,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>145</v>
       </c>
@@ -7070,7 +7187,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>146</v>
       </c>
@@ -7120,7 +7237,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>147</v>
       </c>
@@ -7170,7 +7287,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>148</v>
       </c>
@@ -7220,7 +7337,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>149</v>
       </c>
@@ -7270,7 +7387,7 @@
         <v>-328</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>150</v>
       </c>
@@ -7320,7 +7437,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>151</v>
       </c>
@@ -7370,7 +7487,7 @@
         <v>-369</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>152</v>
       </c>
@@ -7420,7 +7537,7 @@
         <v>-933</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>153</v>
       </c>
@@ -7470,7 +7587,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>154</v>
       </c>
@@ -7520,7 +7637,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>155</v>
       </c>
@@ -7570,7 +7687,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>156</v>
       </c>
@@ -7620,7 +7737,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>157</v>
       </c>
@@ -7670,7 +7787,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>158</v>
       </c>
@@ -7720,7 +7837,7 @@
         <v>-293</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>159</v>
       </c>
@@ -7770,7 +7887,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>160</v>
       </c>
@@ -7820,7 +7937,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>161</v>
       </c>
@@ -7870,7 +7987,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>162</v>
       </c>
@@ -7920,7 +8037,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>163</v>
       </c>
@@ -7970,7 +8087,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>164</v>
       </c>
@@ -8020,7 +8137,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>165</v>
       </c>
@@ -8070,7 +8187,7 @@
         <v>-57</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>166</v>
       </c>
@@ -8120,7 +8237,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>167</v>
       </c>
@@ -8170,7 +8287,7 @@
         <v>-432</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>168</v>
       </c>
@@ -8220,7 +8337,7 @@
         <v>-280</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>169</v>
       </c>
@@ -8270,7 +8387,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>170</v>
       </c>
@@ -8320,7 +8437,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>171</v>
       </c>
@@ -8370,7 +8487,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -8420,7 +8537,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>173</v>
       </c>
@@ -8470,7 +8587,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>174</v>
       </c>
@@ -8520,7 +8637,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>175</v>
       </c>
@@ -8570,7 +8687,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>176</v>
       </c>
@@ -8620,7 +8737,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>177</v>
       </c>
@@ -8670,7 +8787,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>178</v>
       </c>
@@ -8720,7 +8837,7 @@
         <v>-66</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>179</v>
       </c>
@@ -8770,7 +8887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>180</v>
       </c>
@@ -8820,7 +8937,7 @@
         <v>-429</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>181</v>
       </c>
@@ -8870,7 +8987,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>182</v>
       </c>
@@ -8920,7 +9037,7 @@
         <v>-607</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>183</v>
       </c>
@@ -8970,7 +9087,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>184</v>
       </c>
@@ -9020,7 +9137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>185</v>
       </c>
@@ -9070,7 +9187,7 @@
         <v>-343</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>186</v>
       </c>
@@ -9120,7 +9237,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>187</v>
       </c>
@@ -9170,7 +9287,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>188</v>
       </c>
@@ -9220,7 +9337,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>189</v>
       </c>
@@ -9270,7 +9387,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>190</v>
       </c>
@@ -9320,7 +9437,7 @@
         <v>-409</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>191</v>
       </c>
@@ -9370,7 +9487,7 @@
         <v>-373</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>192</v>
       </c>
@@ -9420,7 +9537,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>193</v>
       </c>
@@ -9470,7 +9587,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>194</v>
       </c>
@@ -9520,7 +9637,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>195</v>
       </c>
@@ -9570,7 +9687,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>196</v>
       </c>
@@ -9620,7 +9737,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>197</v>
       </c>
@@ -9670,7 +9787,7 @@
         <v>-743</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>198</v>
       </c>
@@ -9720,7 +9837,7 @@
         <v>-491</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>199</v>
       </c>
@@ -9770,7 +9887,7 @@
         <v>-103</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>200</v>
       </c>
@@ -9820,7 +9937,7 @@
         <v>-826</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>201</v>
       </c>
@@ -9870,7 +9987,7 @@
         <v>-247</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>202</v>
       </c>
@@ -9920,7 +10037,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>203</v>
       </c>
@@ -9970,7 +10087,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>204</v>
       </c>
@@ -10020,7 +10137,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>205</v>
       </c>
@@ -10070,7 +10187,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>206</v>
       </c>
@@ -10120,7 +10237,7 @@
         <v>-179</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>207</v>
       </c>
@@ -10170,7 +10287,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>208</v>
       </c>
@@ -10220,7 +10337,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>209</v>
       </c>
@@ -10270,7 +10387,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>210</v>
       </c>
@@ -10320,7 +10437,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>211</v>
       </c>
@@ -10370,7 +10487,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>212</v>
       </c>
@@ -10420,7 +10537,7 @@
         <v>-292</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>213</v>
       </c>
@@ -10470,7 +10587,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>214</v>
       </c>
@@ -10520,7 +10637,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>215</v>
       </c>
@@ -10570,7 +10687,7 @@
         <v>-235</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>216</v>
       </c>
@@ -10620,7 +10737,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>217</v>
       </c>
@@ -10670,7 +10787,7 @@
         <v>-205</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>218</v>
       </c>
@@ -10720,7 +10837,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>219</v>
       </c>
@@ -10746,7 +10863,7 @@
         <v>828167</v>
       </c>
       <c r="I207">
-        <v>1263.63</v>
+        <v>1263.6300000000001</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -10770,7 +10887,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>220</v>
       </c>
@@ -10820,7 +10937,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>221</v>
       </c>
@@ -10846,7 +10963,7 @@
         <v>1459129</v>
       </c>
       <c r="I209">
-        <v>1291.38</v>
+        <v>1291.3800000000001</v>
       </c>
       <c r="J209">
         <v>0</v>
@@ -10870,7 +10987,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>222</v>
       </c>
@@ -10896,7 +11013,7 @@
         <v>1009904</v>
       </c>
       <c r="I210">
-        <v>1264.64</v>
+        <v>1264.6400000000001</v>
       </c>
       <c r="J210">
         <v>1</v>
@@ -10920,7 +11037,7 @@
         <v>-231</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>223</v>
       </c>
@@ -10946,7 +11063,7 @@
         <v>1127435</v>
       </c>
       <c r="I211">
-        <v>1279.6</v>
+        <v>1279.5999999999999</v>
       </c>
       <c r="J211">
         <v>1</v>
@@ -10970,7 +11087,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>224</v>
       </c>
@@ -11020,7 +11137,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>225</v>
       </c>
@@ -11070,7 +11187,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>226</v>
       </c>
@@ -11120,7 +11237,7 @@
         <v>-149</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>227</v>
       </c>
@@ -11170,7 +11287,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>228</v>
       </c>
@@ -11220,7 +11337,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>229</v>
       </c>
@@ -11270,7 +11387,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>230</v>
       </c>
@@ -11320,7 +11437,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>231</v>
       </c>
@@ -11370,7 +11487,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>232</v>
       </c>
@@ -11420,7 +11537,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>233</v>
       </c>
@@ -11470,7 +11587,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>234</v>
       </c>
@@ -11520,7 +11637,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>235</v>
       </c>
@@ -11570,7 +11687,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>236</v>
       </c>
@@ -11620,7 +11737,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>237</v>
       </c>
@@ -11670,7 +11787,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>238</v>
       </c>
@@ -11720,7 +11837,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>239</v>
       </c>
@@ -11770,7 +11887,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>240</v>
       </c>
@@ -11820,7 +11937,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>241</v>
       </c>
@@ -11846,7 +11963,7 @@
         <v>1224789</v>
       </c>
       <c r="I229">
-        <v>1252.6</v>
+        <v>1252.5999999999999</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -11870,7 +11987,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>242</v>
       </c>
@@ -11896,7 +12013,7 @@
         <v>1261612</v>
       </c>
       <c r="I230">
-        <v>1261.41</v>
+        <v>1261.4100000000001</v>
       </c>
       <c r="J230">
         <v>1</v>
@@ -11920,7 +12037,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>243</v>
       </c>
@@ -11970,7 +12087,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>244</v>
       </c>
@@ -11996,7 +12113,7 @@
         <v>1066465</v>
       </c>
       <c r="I232">
-        <v>1251.12</v>
+        <v>1251.1199999999999</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -12020,7 +12137,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>245</v>
       </c>
@@ -12070,7 +12187,7 @@
         <v>-693</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>246</v>
       </c>
@@ -12120,7 +12237,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>247</v>
       </c>
@@ -12170,7 +12287,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>248</v>
       </c>
@@ -12196,7 +12313,7 @@
         <v>1014924</v>
       </c>
       <c r="I236">
-        <v>1296.89</v>
+        <v>1296.8900000000001</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -12220,7 +12337,7 @@
         <v>-79</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>249</v>
       </c>
@@ -12270,7 +12387,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>250</v>
       </c>
@@ -12296,7 +12413,7 @@
         <v>830148</v>
       </c>
       <c r="I238">
-        <v>1283.62</v>
+        <v>1283.6199999999999</v>
       </c>
       <c r="J238">
         <v>1</v>
@@ -12320,7 +12437,7 @@
         <v>-481</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>251</v>
       </c>
@@ -12370,7 +12487,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>252</v>
       </c>
@@ -12420,7 +12537,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>253</v>
       </c>
@@ -12470,7 +12587,7 @@
         <v>-402</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>254</v>
       </c>
@@ -12520,7 +12637,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>255</v>
       </c>
@@ -12570,7 +12687,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>256</v>
       </c>
@@ -12620,7 +12737,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>257</v>
       </c>
@@ -12670,7 +12787,7 @@
         <v>-553</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>258</v>
       </c>
@@ -12720,7 +12837,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>259</v>
       </c>
@@ -12770,7 +12887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>260</v>
       </c>
@@ -12796,7 +12913,7 @@
         <v>879918</v>
       </c>
       <c r="I248">
-        <v>1305.41</v>
+        <v>1305.4100000000001</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -12820,7 +12937,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>261</v>
       </c>
@@ -12846,7 +12963,7 @@
         <v>719083</v>
       </c>
       <c r="I249">
-        <v>1268.88</v>
+        <v>1268.8800000000001</v>
       </c>
       <c r="J249">
         <v>1</v>
@@ -12870,7 +12987,7 @@
         <v>-69</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>262</v>
       </c>
@@ -12920,7 +13037,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>263</v>
       </c>
@@ -12970,7 +13087,7 @@
         <v>-168</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>264</v>
       </c>
@@ -13020,7 +13137,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>265</v>
       </c>
@@ -13070,7 +13187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>266</v>
       </c>
@@ -13120,7 +13237,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>267</v>
       </c>
@@ -13170,7 +13287,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>268</v>
       </c>
@@ -13196,7 +13313,7 @@
         <v>815010</v>
       </c>
       <c r="I256">
-        <v>1183.09</v>
+        <v>1183.0899999999999</v>
       </c>
       <c r="J256">
         <v>1</v>
@@ -13220,7 +13337,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="257" spans="1:16">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>269</v>
       </c>
@@ -13270,7 +13387,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:16">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>270</v>
       </c>
@@ -13296,7 +13413,7 @@
         <v>871678</v>
       </c>
       <c r="I258">
-        <v>1140.84</v>
+        <v>1140.8399999999999</v>
       </c>
       <c r="J258">
         <v>1</v>
@@ -13320,7 +13437,7 @@
         <v>-522</v>
       </c>
     </row>
-    <row r="259" spans="1:16">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>271</v>
       </c>
@@ -13370,7 +13487,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="260" spans="1:16">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>272</v>
       </c>
@@ -13420,7 +13537,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="261" spans="1:16">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>273</v>
       </c>
@@ -13446,7 +13563,7 @@
         <v>746473</v>
       </c>
       <c r="I261">
-        <v>1168.09</v>
+        <v>1168.0899999999999</v>
       </c>
       <c r="J261">
         <v>1</v>
@@ -13470,7 +13587,7 @@
         <v>-572</v>
       </c>
     </row>
-    <row r="262" spans="1:16">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>274</v>
       </c>
@@ -13520,7 +13637,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="263" spans="1:16">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>275</v>
       </c>
@@ -13570,7 +13687,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="264" spans="1:16">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>276</v>
       </c>
@@ -13620,7 +13737,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="265" spans="1:16">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>277</v>
       </c>
@@ -13670,7 +13787,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="266" spans="1:16">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>278</v>
       </c>
@@ -13696,7 +13813,7 @@
         <v>706853</v>
       </c>
       <c r="I266">
-        <v>1137.15</v>
+        <v>1137.1500000000001</v>
       </c>
       <c r="J266">
         <v>1</v>
@@ -13720,7 +13837,7 @@
         <v>-715</v>
       </c>
     </row>
-    <row r="267" spans="1:16">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>279</v>
       </c>
@@ -13770,7 +13887,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="268" spans="1:16">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>280</v>
       </c>
@@ -13820,7 +13937,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="269" spans="1:16">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>281</v>
       </c>
@@ -13846,7 +13963,7 @@
         <v>736507</v>
       </c>
       <c r="I269">
-        <v>1103.16</v>
+        <v>1103.1600000000001</v>
       </c>
       <c r="J269">
         <v>1</v>
@@ -13870,7 +13987,7 @@
         <v>-276</v>
       </c>
     </row>
-    <row r="270" spans="1:16">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>282</v>
       </c>
@@ -13920,7 +14037,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="271" spans="1:16">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>283</v>
       </c>
@@ -13970,7 +14087,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="272" spans="1:16">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>284</v>
       </c>
@@ -14020,7 +14137,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="273" spans="1:16">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>285</v>
       </c>
@@ -14070,7 +14187,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="274" spans="1:16">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>286</v>
       </c>
@@ -14120,7 +14237,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="275" spans="1:16">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>287</v>
       </c>
@@ -14170,7 +14287,7 @@
         <v>-436</v>
       </c>
     </row>
-    <row r="276" spans="1:16">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>288</v>
       </c>
@@ -14220,7 +14337,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="277" spans="1:16">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>289</v>
       </c>
@@ -14270,7 +14387,7 @@
         <v>-458</v>
       </c>
     </row>
-    <row r="278" spans="1:16">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>290</v>
       </c>
@@ -14320,7 +14437,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="279" spans="1:16">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>291</v>
       </c>
@@ -14370,7 +14487,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="280" spans="1:16">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>292</v>
       </c>
@@ -14420,7 +14537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="281" spans="1:16">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>293</v>
       </c>
@@ -14446,7 +14563,7 @@
         <v>881571</v>
       </c>
       <c r="I281">
-        <v>975.1900000000001</v>
+        <v>975.19</v>
       </c>
       <c r="J281">
         <v>0</v>
@@ -14470,7 +14587,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="282" spans="1:16">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>294</v>
       </c>
@@ -14496,7 +14613,7 @@
         <v>931363</v>
       </c>
       <c r="I282">
-        <v>964.6799999999999</v>
+        <v>964.68</v>
       </c>
       <c r="J282">
         <v>0</v>
@@ -14520,7 +14637,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="283" spans="1:16">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>295</v>
       </c>
@@ -14570,7 +14687,7 @@
         <v>-536</v>
       </c>
     </row>
-    <row r="284" spans="1:16">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>296</v>
       </c>
@@ -14620,7 +14737,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="285" spans="1:16">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>297</v>
       </c>
@@ -14646,7 +14763,7 @@
         <v>617560</v>
       </c>
       <c r="I285">
-        <v>929.9400000000001</v>
+        <v>929.94</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -14670,7 +14787,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="286" spans="1:16">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>298</v>
       </c>
@@ -14720,7 +14837,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="287" spans="1:16">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>299</v>
       </c>
@@ -14770,7 +14887,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="288" spans="1:16">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>300</v>
       </c>
@@ -14820,7 +14937,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>301</v>
       </c>
@@ -14870,7 +14987,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>302</v>
       </c>
@@ -14896,7 +15013,7 @@
         <v>704369</v>
       </c>
       <c r="I290">
-        <v>879.3099999999999</v>
+        <v>879.31</v>
       </c>
       <c r="J290">
         <v>0</v>
@@ -14920,7 +15037,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>303</v>
       </c>
@@ -14970,7 +15087,7 @@
         <v>-168</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>304</v>
       </c>
@@ -14996,7 +15113,7 @@
         <v>728532</v>
       </c>
       <c r="I292">
-        <v>875.4299999999999</v>
+        <v>875.43</v>
       </c>
       <c r="J292">
         <v>1</v>
@@ -15020,7 +15137,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>305</v>
       </c>
@@ -15046,7 +15163,7 @@
         <v>883903</v>
       </c>
       <c r="I293">
-        <v>923.1900000000001</v>
+        <v>923.19</v>
       </c>
       <c r="J293">
         <v>0</v>
@@ -15070,7 +15187,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>306</v>
       </c>
@@ -15120,7 +15237,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>307</v>
       </c>
@@ -15170,7 +15287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>308</v>
       </c>
@@ -15220,7 +15337,7 @@
         <v>-225</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>309</v>
       </c>
@@ -15270,7 +15387,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>310</v>
       </c>
@@ -15320,7 +15437,7 @@
         <v>-369</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>311</v>
       </c>
@@ -15346,7 +15463,7 @@
         <v>602910</v>
       </c>
       <c r="I299">
-        <v>1040.62</v>
+        <v>1040.6199999999999</v>
       </c>
       <c r="J299">
         <v>0</v>
@@ -15370,7 +15487,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>312</v>
       </c>
@@ -15396,7 +15513,7 @@
         <v>927525</v>
       </c>
       <c r="I300">
-        <v>1044.15</v>
+        <v>1044.1500000000001</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -15420,7 +15537,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>313</v>
       </c>
@@ -15470,7 +15587,7 @@
         <v>-381</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>314</v>
       </c>
@@ -15520,7 +15637,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>315</v>
       </c>
@@ -15570,7 +15687,7 @@
         <v>-260</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>316</v>
       </c>
@@ -15620,7 +15737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>317</v>
       </c>
@@ -15670,7 +15787,7 @@
         <v>-126</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>318</v>
       </c>
@@ -15720,7 +15837,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>319</v>
       </c>
@@ -15770,7 +15887,7 @@
         <v>-196</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>320</v>
       </c>
@@ -15820,7 +15937,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>321</v>
       </c>
@@ -15870,7 +15987,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>322</v>
       </c>
@@ -15920,7 +16037,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>323</v>
       </c>
@@ -15970,7 +16087,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>324</v>
       </c>
@@ -16020,7 +16137,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>325</v>
       </c>
@@ -16070,7 +16187,7 @@
         <v>-326</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>326</v>
       </c>
@@ -16096,7 +16213,7 @@
         <v>782172</v>
       </c>
       <c r="I314">
-        <v>794.9400000000001</v>
+        <v>794.94</v>
       </c>
       <c r="J314">
         <v>1</v>
@@ -16120,7 +16237,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>327</v>
       </c>
@@ -16170,7 +16287,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>328</v>
       </c>
@@ -16196,7 +16313,7 @@
         <v>781680</v>
       </c>
       <c r="I316">
-        <v>795.8099999999999</v>
+        <v>795.81</v>
       </c>
       <c r="J316">
         <v>0</v>
@@ -16220,7 +16337,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>329</v>
       </c>
@@ -16270,7 +16387,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>330</v>
       </c>
@@ -16320,7 +16437,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>331</v>
       </c>
@@ -16370,7 +16487,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>332</v>
       </c>
@@ -16420,7 +16537,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="321" spans="1:16">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>333</v>
       </c>
@@ -16446,7 +16563,7 @@
         <v>629061</v>
       </c>
       <c r="I321">
-        <v>738.1900000000001</v>
+        <v>738.19</v>
       </c>
       <c r="J321">
         <v>0</v>
@@ -16470,7 +16587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:16">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>334</v>
       </c>
@@ -16520,7 +16637,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="323" spans="1:16">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>335</v>
       </c>
@@ -16570,7 +16687,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="324" spans="1:16">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>336</v>
       </c>
@@ -16620,7 +16737,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="325" spans="1:16">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>337</v>
       </c>
@@ -16670,7 +16787,7 @@
         <v>-118</v>
       </c>
     </row>
-    <row r="326" spans="1:16">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>338</v>
       </c>
@@ -16720,7 +16837,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="327" spans="1:16">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>339</v>
       </c>
@@ -16770,7 +16887,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="328" spans="1:16">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>340</v>
       </c>
@@ -16820,7 +16937,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="329" spans="1:16">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>341</v>
       </c>
@@ -16870,7 +16987,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="330" spans="1:16">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>342</v>
       </c>
@@ -16920,7 +17037,7 @@
         <v>-271</v>
       </c>
     </row>
-    <row r="331" spans="1:16">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>343</v>
       </c>
@@ -16970,7 +17087,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="332" spans="1:16">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>344</v>
       </c>
@@ -16996,7 +17113,7 @@
         <v>676614</v>
       </c>
       <c r="I332">
-        <v>798.4400000000001</v>
+        <v>798.44</v>
       </c>
       <c r="J332">
         <v>0</v>
@@ -17020,7 +17137,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="333" spans="1:16">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>345</v>
       </c>
@@ -17070,7 +17187,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="334" spans="1:16">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>346</v>
       </c>
@@ -17120,7 +17237,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="335" spans="1:16">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>347</v>
       </c>
@@ -17170,7 +17287,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="336" spans="1:16">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>348</v>
       </c>
@@ -17220,7 +17337,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>349</v>
       </c>
@@ -17270,7 +17387,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>350</v>
       </c>
@@ -17320,7 +17437,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>351</v>
       </c>
@@ -17370,7 +17487,7 @@
         <v>-286</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>352</v>
       </c>
@@ -17420,7 +17537,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>353</v>
       </c>
@@ -17470,7 +17587,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>354</v>
       </c>
@@ -17520,7 +17637,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>355</v>
       </c>
@@ -17570,7 +17687,7 @@
         <v>-215</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>356</v>
       </c>
@@ -17620,7 +17737,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>357</v>
       </c>
@@ -17646,7 +17763,7 @@
         <v>638716</v>
       </c>
       <c r="I345">
-        <v>779.8200000000001</v>
+        <v>779.82</v>
       </c>
       <c r="J345">
         <v>1</v>
@@ -17670,7 +17787,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>358</v>
       </c>
@@ -17720,7 +17837,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>359</v>
       </c>
@@ -17746,7 +17863,7 @@
         <v>823677</v>
       </c>
       <c r="I347">
-        <v>829.4299999999999</v>
+        <v>829.43</v>
       </c>
       <c r="J347">
         <v>0</v>
@@ -17770,7 +17887,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>360</v>
       </c>
@@ -17820,7 +17937,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>361</v>
       </c>
@@ -17870,7 +17987,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>362</v>
       </c>
@@ -17920,7 +18037,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>363</v>
       </c>
@@ -17970,7 +18087,7 @@
         <v>-343</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>364</v>
       </c>
@@ -17996,7 +18113,7 @@
         <v>581774</v>
       </c>
       <c r="I352">
-        <v>866.8099999999999</v>
+        <v>866.81</v>
       </c>
       <c r="J352">
         <v>0</v>
@@ -18020,7 +18137,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="353" spans="1:16">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>365</v>
       </c>
@@ -18070,7 +18187,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="354" spans="1:16">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>366</v>
       </c>
@@ -18120,7 +18237,7 @@
         <v>-141</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>367</v>
       </c>
@@ -18170,7 +18287,7 @@
         <v>-261</v>
       </c>
     </row>
-    <row r="356" spans="1:16">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>368</v>
       </c>
@@ -18220,7 +18337,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="357" spans="1:16">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>369</v>
       </c>
@@ -18246,7 +18363,7 @@
         <v>925707</v>
       </c>
       <c r="I357">
-        <v>1228.63</v>
+        <v>1228.6300000000001</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -18270,7 +18387,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="358" spans="1:16">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>370</v>
       </c>
@@ -18320,7 +18437,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="359" spans="1:16">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>371</v>
       </c>
@@ -18370,7 +18487,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="360" spans="1:16">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>372</v>
       </c>
@@ -18420,7 +18537,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="361" spans="1:16">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>373</v>
       </c>
@@ -18470,7 +18587,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="362" spans="1:16">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>374</v>
       </c>
@@ -18520,7 +18637,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="363" spans="1:16">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>375</v>
       </c>
@@ -18570,7 +18687,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="364" spans="1:16">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>376</v>
       </c>
@@ -18620,7 +18737,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="365" spans="1:16">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>377</v>
       </c>
@@ -18670,7 +18787,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="366" spans="1:16">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>378</v>
       </c>
@@ -18720,7 +18837,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="367" spans="1:16">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>379</v>
       </c>
@@ -18770,7 +18887,7 @@
         <v>-148</v>
       </c>
     </row>
-    <row r="368" spans="1:16">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>380</v>
       </c>
@@ -18820,7 +18937,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>381</v>
       </c>
@@ -18870,7 +18987,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>382</v>
       </c>
@@ -18920,7 +19037,7 @@
         <v>-548</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>383</v>
       </c>
@@ -18970,7 +19087,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>384</v>
       </c>
@@ -19020,7 +19137,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>385</v>
       </c>
@@ -19070,7 +19187,7 @@
         <v>-961</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>386</v>
       </c>
@@ -19120,7 +19237,7 @@
         <v>-333</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>387</v>
       </c>
@@ -19170,7 +19287,7 @@
         <v>-116</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>388</v>
       </c>
@@ -19220,7 +19337,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>389</v>
       </c>
@@ -19270,7 +19387,7 @@
         <v>-168</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>390</v>
       </c>
@@ -19320,7 +19437,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>391</v>
       </c>
@@ -19370,7 +19487,7 @@
         <v>-435</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>392</v>
       </c>
@@ -19420,7 +19537,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>393</v>
       </c>
@@ -19470,7 +19587,7 @@
         <v>-488</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>394</v>
       </c>
@@ -19520,7 +19637,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>395</v>
       </c>
@@ -19546,7 +19663,7 @@
         <v>305076</v>
       </c>
       <c r="I383">
-        <v>1282.62</v>
+        <v>1282.6199999999999</v>
       </c>
       <c r="J383">
         <v>0</v>
@@ -19570,7 +19687,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>396</v>
       </c>
@@ -19596,7 +19713,7 @@
         <v>464865</v>
       </c>
       <c r="I384">
-        <v>1253.15</v>
+        <v>1253.1500000000001</v>
       </c>
       <c r="J384">
         <v>0</v>
@@ -19620,7 +19737,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>397</v>
       </c>
@@ -19646,7 +19763,7 @@
         <v>723640</v>
       </c>
       <c r="I385">
-        <v>1268.14</v>
+        <v>1268.1400000000001</v>
       </c>
       <c r="J385">
         <v>1</v>
@@ -19670,7 +19787,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>398</v>
       </c>
@@ -19696,7 +19813,7 @@
         <v>374431</v>
       </c>
       <c r="I386">
-        <v>1254.91</v>
+        <v>1254.9100000000001</v>
       </c>
       <c r="J386">
         <v>0</v>
@@ -19720,7 +19837,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>399</v>
       </c>
@@ -19746,7 +19863,7 @@
         <v>378225</v>
       </c>
       <c r="I387">
-        <v>1213.85</v>
+        <v>1213.8499999999999</v>
       </c>
       <c r="J387">
         <v>1</v>
@@ -19770,7 +19887,7 @@
         <v>-404</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>400</v>
       </c>
@@ -19796,7 +19913,7 @@
         <v>532405</v>
       </c>
       <c r="I388">
-        <v>1214.36</v>
+        <v>1214.3599999999999</v>
       </c>
       <c r="J388">
         <v>0</v>
@@ -19820,7 +19937,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>401</v>
       </c>
@@ -19846,7 +19963,7 @@
         <v>416044</v>
       </c>
       <c r="I389">
-        <v>1202.62</v>
+        <v>1202.6199999999999</v>
       </c>
       <c r="J389">
         <v>0</v>
@@ -19870,7 +19987,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>402</v>
       </c>
@@ -19896,7 +20013,7 @@
         <v>543040</v>
       </c>
       <c r="I390">
-        <v>1187.15</v>
+        <v>1187.1500000000001</v>
       </c>
       <c r="J390">
         <v>1</v>
@@ -19920,7 +20037,7 @@
         <v>-163</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>403</v>
       </c>
@@ -19970,7 +20087,7 @@
         <v>-226</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>404</v>
       </c>
@@ -20020,7 +20137,7 @@
         <v>-389</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>405</v>
       </c>
@@ -20046,7 +20163,7 @@
         <v>412174</v>
       </c>
       <c r="I393">
-        <v>1152.63</v>
+        <v>1152.6300000000001</v>
       </c>
       <c r="J393">
         <v>0</v>
@@ -20070,7 +20187,7 @@
         <v>-248</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>406</v>
       </c>
@@ -20096,7 +20213,7 @@
         <v>522071</v>
       </c>
       <c r="I394">
-        <v>1132.87</v>
+        <v>1132.8699999999999</v>
       </c>
       <c r="J394">
         <v>1</v>
@@ -20120,7 +20237,7 @@
         <v>-394</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>407</v>
       </c>
@@ -20170,7 +20287,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>408</v>
       </c>
@@ -20196,7 +20313,7 @@
         <v>913243</v>
       </c>
       <c r="I396">
-        <v>1215.88</v>
+        <v>1215.8800000000001</v>
       </c>
       <c r="J396">
         <v>1</v>
@@ -20220,7 +20337,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>409</v>
       </c>
@@ -20270,7 +20387,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>410</v>
       </c>
@@ -20296,7 +20413,7 @@
         <v>798872</v>
       </c>
       <c r="I398">
-        <v>1304.37</v>
+        <v>1304.3699999999999</v>
       </c>
       <c r="J398">
         <v>0</v>
@@ -20320,7 +20437,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>411</v>
       </c>
@@ -20370,7 +20487,7 @@
         <v>-348</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>412</v>
       </c>
@@ -20396,7 +20513,7 @@
         <v>468369</v>
       </c>
       <c r="I400">
-        <v>1266.64</v>
+        <v>1266.6400000000001</v>
       </c>
       <c r="J400">
         <v>1</v>
@@ -20420,7 +20537,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>413</v>
       </c>
@@ -20470,7 +20587,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>414</v>
       </c>
@@ -20520,7 +20637,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>415</v>
       </c>
@@ -20570,7 +20687,7 @@
         <v>-280</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>416</v>
       </c>
@@ -20596,7 +20713,7 @@
         <v>623615</v>
       </c>
       <c r="I404">
-        <v>1250.15</v>
+        <v>1250.1500000000001</v>
       </c>
       <c r="J404">
         <v>0</v>
@@ -20620,7 +20737,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>417</v>
       </c>
@@ -20670,7 +20787,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>418</v>
       </c>
@@ -20720,7 +20837,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>419</v>
       </c>
@@ -20770,7 +20887,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>420</v>
       </c>
@@ -20820,7 +20937,7 @@
         <v>-209</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>421</v>
       </c>
@@ -20870,7 +20987,7 @@
         <v>-527</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>422</v>
       </c>
@@ -20896,7 +21013,7 @@
         <v>476742</v>
       </c>
       <c r="I410">
-        <v>1207.15</v>
+        <v>1207.1500000000001</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -20920,7 +21037,7 @@
         <v>-311</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>423</v>
       </c>
@@ -20970,7 +21087,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>424</v>
       </c>
@@ -21020,7 +21137,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>425</v>
       </c>
@@ -21070,7 +21187,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>426</v>
       </c>
@@ -21120,7 +21237,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>427</v>
       </c>
@@ -21170,7 +21287,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>428</v>
       </c>
@@ -21196,7 +21313,7 @@
         <v>426061</v>
       </c>
       <c r="I416">
-        <v>1201.38</v>
+        <v>1201.3800000000001</v>
       </c>
       <c r="J416">
         <v>1</v>
@@ -21220,7 +21337,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>429</v>
       </c>
@@ -21246,7 +21363,7 @@
         <v>392813</v>
       </c>
       <c r="I417">
-        <v>1167.35</v>
+        <v>1167.3499999999999</v>
       </c>
       <c r="J417">
         <v>1</v>
@@ -21270,7 +21387,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>430</v>
       </c>
@@ -21320,7 +21437,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>431</v>
       </c>
@@ -21370,7 +21487,7 @@
         <v>-348</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>432</v>
       </c>
@@ -21420,7 +21537,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>433</v>
       </c>
@@ -21470,7 +21587,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>434</v>
       </c>
@@ -21520,7 +21637,7 @@
         <v>-272</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>435</v>
       </c>
@@ -21546,7 +21663,7 @@
         <v>427434</v>
       </c>
       <c r="I423">
-        <v>1099.38</v>
+        <v>1099.3800000000001</v>
       </c>
       <c r="J423">
         <v>0</v>
@@ -21570,7 +21687,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>436</v>
       </c>
@@ -21620,7 +21737,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>437</v>
       </c>
@@ -21670,7 +21787,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>438</v>
       </c>
@@ -21696,7 +21813,7 @@
         <v>366280</v>
       </c>
       <c r="I426">
-        <v>1102.86</v>
+        <v>1102.8599999999999</v>
       </c>
       <c r="J426">
         <v>0</v>
@@ -21720,7 +21837,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>439</v>
       </c>
@@ -21770,7 +21887,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>440</v>
       </c>
@@ -21820,7 +21937,7 @@
         <v>-284</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>441</v>
       </c>
@@ -21870,7 +21987,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>442</v>
       </c>
@@ -21920,7 +22037,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>443</v>
       </c>
@@ -21973,4 +22090,836 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B18F5A-9464-487D-B220-8943EFB013D8}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="6">
+        <f>SUM(K:K)</f>
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45566</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1010.59</v>
+      </c>
+      <c r="D2" s="4">
+        <f>ROUND(C2/3,0)</f>
+        <v>337</v>
+      </c>
+      <c r="E2" s="4">
+        <f>ROUND(C2*2/3,0)</f>
+        <v>674</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="4">
+        <v>93033</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(F2="long",G2-D2,G2+D2)</f>
+        <v>92696</v>
+      </c>
+      <c r="I2" s="4">
+        <f>IF(F2="long",G2+E2,G2-E2)</f>
+        <v>93707</v>
+      </c>
+      <c r="J2" s="4">
+        <v>93707</v>
+      </c>
+      <c r="K2" s="4">
+        <f>IF(J2=0,0,IF(F2="long",J2-G2,G2-J2))</f>
+        <v>674</v>
+      </c>
+      <c r="N2" s="6">
+        <f>N1*4</f>
+        <v>10096</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45567</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1012.69</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D20" si="0">ROUND(C3/3,0)</f>
+        <v>338</v>
+      </c>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E20" si="1">ROUND(C3*2/3,0)</f>
+        <v>675</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4">
+        <v>93701</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H20" si="2">IF(F3="long",G3-D3,G3+D3)</f>
+        <v>93363</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I20" si="3">IF(F3="long",G3+E3,G3-E3)</f>
+        <v>94376</v>
+      </c>
+      <c r="J3" s="4">
+        <v>94376</v>
+      </c>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K20" si="4">IF(J3=0,0,IF(F3="long",J3-G3,G3-J3))</f>
+        <v>675</v>
+      </c>
+      <c r="N3" s="6">
+        <f>N1*8</f>
+        <v>20192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45568</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1002.5</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>334</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>668</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4">
+        <v>94400</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
+        <v>94066</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="3"/>
+        <v>95068</v>
+      </c>
+      <c r="J4" s="4">
+        <v>94066</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="4"/>
+        <v>-334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45569</v>
+      </c>
+      <c r="C5" s="5">
+        <v>988.82</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>330</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="1"/>
+        <v>659</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4">
+        <v>94300</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="2"/>
+        <v>94630</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="3"/>
+        <v>93641</v>
+      </c>
+      <c r="J5" s="4">
+        <v>94630</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="4"/>
+        <v>-330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45572</v>
+      </c>
+      <c r="C6" s="5">
+        <v>997.69</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>333</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>665</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="4">
+        <v>94645</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>94312</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="3"/>
+        <v>95310</v>
+      </c>
+      <c r="J6" s="4">
+        <v>95310</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="4"/>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45573</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1011.07</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>337</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="1"/>
+        <v>674</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="4">
+        <v>95554</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="2"/>
+        <v>95217</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="3"/>
+        <v>96228</v>
+      </c>
+      <c r="J7" s="4">
+        <v>95217</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="4"/>
+        <v>-337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45574</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1006.42</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>335</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>671</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="4">
+        <v>95850</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>95515</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="3"/>
+        <v>96521</v>
+      </c>
+      <c r="J8" s="4">
+        <v>95994</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45575</v>
+      </c>
+      <c r="C9" s="5">
+        <v>993.61</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="0"/>
+        <v>331</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="1"/>
+        <v>662</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4">
+        <v>96024</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="2"/>
+        <v>95693</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="3"/>
+        <v>96686</v>
+      </c>
+      <c r="J9" s="4">
+        <v>95693</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="4"/>
+        <v>-331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45576</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1011.92</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>337</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>675</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="4">
+        <v>95161</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>95498</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="3"/>
+        <v>94486</v>
+      </c>
+      <c r="J10" s="4">
+        <v>94486</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="4"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45579</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1026.57</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="0"/>
+        <v>342</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="4">
+        <v>94961</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="2"/>
+        <v>95303</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="3"/>
+        <v>94277</v>
+      </c>
+      <c r="J11" s="4">
+        <v>95026</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="4"/>
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45580</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1013.39</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>338</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="1"/>
+        <v>676</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="4">
+        <v>95080</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="2"/>
+        <v>94742</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="3"/>
+        <v>95756</v>
+      </c>
+      <c r="J12" s="4">
+        <v>95756</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="4"/>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45581</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1063.5</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="0"/>
+        <v>355</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="1"/>
+        <v>709</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="4">
+        <v>96600</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="2"/>
+        <v>96245</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="3"/>
+        <v>97309</v>
+      </c>
+      <c r="J13" s="4">
+        <v>96245</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="4"/>
+        <v>-355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>45582</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1083.1099999999999</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>361</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>722</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="4">
+        <v>96096</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>96457</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="3"/>
+        <v>95374</v>
+      </c>
+      <c r="J14" s="4">
+        <v>95374</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="4"/>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>45583</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1096.3900000000001</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="0"/>
+        <v>365</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="1"/>
+        <v>731</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="4">
+        <v>95383</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" si="2"/>
+        <v>95748</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="3"/>
+        <v>94652</v>
+      </c>
+      <c r="J15" s="4">
+        <v>94652</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="4"/>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45586</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1093.1500000000001</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>729</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="4">
+        <v>94499</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>94863</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="3"/>
+        <v>93770</v>
+      </c>
+      <c r="J16" s="4">
+        <v>94863</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="4"/>
+        <v>-364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45587</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1090.56</v>
+      </c>
+      <c r="D17" s="4">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" si="1"/>
+        <v>727</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="4">
+        <v>95218</v>
+      </c>
+      <c r="H17" s="4">
+        <f t="shared" si="2"/>
+        <v>94854</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="3"/>
+        <v>95945</v>
+      </c>
+      <c r="J17" s="4">
+        <v>95945</v>
+      </c>
+      <c r="K17" s="4">
+        <f t="shared" si="4"/>
+        <v>727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45588</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1069.52</v>
+      </c>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>357</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>713</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="4">
+        <v>95851</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>95494</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="3"/>
+        <v>96564</v>
+      </c>
+      <c r="J18" s="4">
+        <v>95494</v>
+      </c>
+      <c r="K18" s="4">
+        <f t="shared" si="4"/>
+        <v>-357</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>45589</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1043.2</v>
+      </c>
+      <c r="D19" s="4">
+        <f t="shared" si="0"/>
+        <v>348</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="1"/>
+        <v>695</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="4">
+        <v>95372</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" si="2"/>
+        <v>95720</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="3"/>
+        <v>94677</v>
+      </c>
+      <c r="J19" s="4">
+        <v>95720</v>
+      </c>
+      <c r="K19" s="4">
+        <f t="shared" si="4"/>
+        <v>-348</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45590</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1032.19</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>344</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>688</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="4">
+        <v>96140</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>95796</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="3"/>
+        <v>96828</v>
+      </c>
+      <c r="J20" s="4">
+        <v>95796</v>
+      </c>
+      <c r="K20" s="4">
+        <f t="shared" si="4"/>
+        <v>-344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>